--- a/Data_extraction_24_RCT_Joana.xlsx
+++ b/Data_extraction_24_RCT_Joana.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joanarodriguesribeiro/Documents/PhD_UZH_2025_2028/projects/PHD_MID/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F838C0C-523C-4041-AE6C-EF1034F0B618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB86A035-84F5-8749-8559-87CF5FA48E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1900" yWindow="1820" windowWidth="27240" windowHeight="16440" xr2:uid="{73D5A3F7-A23D-D840-93F2-C29B0B0B7D4B}"/>
   </bookViews>
